--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>99990</v>
+        <v>99996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>99996</v>
+        <v>99998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>99998</v>
+        <v>99999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>99999</v>
+        <v>100005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100005</v>
+        <v>100009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100009</v>
+        <v>100011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100011</v>
+        <v>100013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100013</v>
+        <v>100026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100026</v>
+        <v>100028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100028</v>
+        <v>100031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100031</v>
+        <v>100041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100041</v>
+        <v>100042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100042</v>
+        <v>100047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100047</v>
+        <v>100050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100050</v>
+        <v>100056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100056</v>
+        <v>100068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100069</v>
+        <v>100072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100072</v>
+        <v>100073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12932-2023 artfynd.xlsx
+++ b/artfynd/A 12932-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949587</v>
       </c>
       <c r="B2" t="n">
-        <v>100073</v>
+        <v>100076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
